--- a/backend/data/financials_by_company/000090.SZ.xlsx
+++ b/backend/data/financials_by_company/000090.SZ.xlsx
@@ -697,662 +697,662 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-230373737.443557</v>
+        <v>-127679502.421345</v>
       </c>
       <c r="C2" t="n">
-        <v>0.396582</v>
+        <v>0.297417</v>
       </c>
       <c r="D2" t="n">
-        <v>2255253542.32</v>
+        <v>3794332198.36</v>
       </c>
       <c r="E2" t="n">
-        <v>-580897483.71</v>
+        <v>-429294379.19</v>
       </c>
       <c r="F2" t="n">
-        <v>-580897483.71</v>
+        <v>-429294379.19</v>
       </c>
       <c r="G2" t="n">
-        <v>620571968.02</v>
+        <v>1933357215.84</v>
       </c>
       <c r="H2" t="n">
-        <v>402276302.97</v>
+        <v>251694687.84</v>
       </c>
       <c r="I2" t="n">
-        <v>17954869511.73</v>
+        <v>18675894353.81</v>
       </c>
       <c r="J2" t="n">
-        <v>1674356058.61</v>
+        <v>3365037819.17</v>
       </c>
       <c r="K2" t="n">
-        <v>1272079755.64</v>
+        <v>3113343131.33</v>
       </c>
       <c r="L2" t="n">
-        <v>-163606219.45</v>
+        <v>-257177261.08</v>
       </c>
       <c r="M2" t="n">
-        <v>288344589.29</v>
+        <v>335521800.82</v>
       </c>
       <c r="N2" t="n">
-        <v>135529489.11</v>
+        <v>97463343.45999999</v>
       </c>
       <c r="O2" t="n">
-        <v>971095714.286443</v>
+        <v>2234972092.608655</v>
       </c>
       <c r="P2" t="n">
-        <v>620571968.02</v>
+        <v>1933357215.84</v>
       </c>
       <c r="Q2" t="n">
-        <v>19660705793.47</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
+        <v>19855560881.76</v>
+      </c>
+      <c r="R2" t="n">
+        <v>17738124.74</v>
+      </c>
       <c r="S2" t="n">
-        <v>986690844.77</v>
-      </c>
-      <c r="T2" t="inlineStr"/>
+        <v>2807736737.39</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2012655857</v>
+      </c>
       <c r="U2" t="n">
-        <v>2371310539</v>
+        <v>2012655857</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2617</v>
+        <v>0.9606</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2617</v>
+        <v>0.9606</v>
       </c>
       <c r="X2" t="n">
-        <v>620571968.02</v>
+        <v>1933357215.84</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>620571968.02</v>
+        <v>1933357215.84</v>
       </c>
       <c r="AA2" t="n">
-        <v>26968887.42</v>
+        <v>-18292465.36</v>
       </c>
       <c r="AB2" t="n">
-        <v>593603080.6</v>
+        <v>1951649681.2</v>
       </c>
       <c r="AC2" t="n">
-        <v>593603080.6</v>
+        <v>1951649681.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>390132085.75</v>
+        <v>826171649.3099999</v>
       </c>
       <c r="AE2" t="n">
-        <v>983735166.35</v>
+        <v>2777821330.51</v>
       </c>
       <c r="AF2" t="n">
-        <v>-2955678.42</v>
+        <v>-29915406.88</v>
       </c>
       <c r="AG2" t="n">
-        <v>-580897483.71</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-5755100.55</v>
-      </c>
+        <v>-431343957.35</v>
+      </c>
+      <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="n">
-        <v>59967587.92</v>
+        <v>119127650.01</v>
       </c>
       <c r="AJ2" t="n">
-        <v>526684996.34</v>
+        <v>312216307.34</v>
       </c>
       <c r="AK2" t="n">
-        <v>-163606219.45</v>
+        <v>-257177261.08</v>
       </c>
       <c r="AL2" t="n">
-        <v>10791119.27</v>
+        <v>19118803.72</v>
       </c>
       <c r="AM2" t="n">
-        <v>288344589.29</v>
+        <v>335521800.82</v>
       </c>
       <c r="AN2" t="n">
-        <v>135529489.11</v>
+        <v>97463343.45999999</v>
       </c>
       <c r="AO2" t="n">
-        <v>1696648465.19</v>
+        <v>3413770989.3</v>
       </c>
       <c r="AP2" t="n">
-        <v>1705836281.74</v>
+        <v>1179666527.95</v>
       </c>
       <c r="AQ2" t="n">
-        <v>505451080.98</v>
+        <v>137684332.48</v>
       </c>
       <c r="AR2" t="n">
-        <v>81609075.92</v>
+        <v>33023077.17</v>
       </c>
       <c r="AS2" t="n">
-        <v>41674247.76</v>
+        <v>16873058.24</v>
       </c>
       <c r="AT2" t="n">
-        <v>39934828.16</v>
+        <v>16150018.93</v>
       </c>
       <c r="AU2" t="n">
-        <v>500641329.77</v>
+        <v>416461502.81</v>
       </c>
       <c r="AV2" t="n">
-        <v>330165878.32</v>
+        <v>295235866.93</v>
       </c>
       <c r="AW2" t="n">
-        <v>261830170.99</v>
+        <v>211986058.76</v>
       </c>
       <c r="AX2" t="n">
-        <v>68335707.33</v>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+        <v>83249808.17</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>17738124.74</v>
+      </c>
       <c r="AZ2" t="n">
-        <v>3402484746.93</v>
+        <v>4593437517.25</v>
       </c>
       <c r="BA2" t="n">
-        <v>17954869511.73</v>
+        <v>18675894353.81</v>
       </c>
       <c r="BB2" t="n">
-        <v>21357354258.66</v>
+        <v>23269331871.06</v>
       </c>
       <c r="BC2" t="n">
-        <v>21357354258.66</v>
+        <v>23269331871.06</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-32221818.584355</v>
+        <v>-214220309.462309</v>
       </c>
       <c r="C3" t="n">
-        <v>0.245498</v>
+        <v>0.298917</v>
       </c>
       <c r="D3" t="n">
-        <v>2897104832.86</v>
+        <v>4340959626.73</v>
       </c>
       <c r="E3" t="n">
-        <v>-131250933.78</v>
+        <v>-716653780.28</v>
       </c>
       <c r="F3" t="n">
-        <v>-131250933.78</v>
+        <v>-716653780.28</v>
       </c>
       <c r="G3" t="n">
-        <v>1517014757.66</v>
+        <v>1951844361.82</v>
       </c>
       <c r="H3" t="n">
-        <v>448467547.89</v>
+        <v>355386247.08</v>
       </c>
       <c r="I3" t="n">
-        <v>23056841743.9</v>
+        <v>21078030233.08</v>
       </c>
       <c r="J3" t="n">
-        <v>2765853899.08</v>
+        <v>3624305846.45</v>
       </c>
       <c r="K3" t="n">
-        <v>2317386351.19</v>
+        <v>3268919599.37</v>
       </c>
       <c r="L3" t="n">
-        <v>-242831762.26</v>
+        <v>-379720508.56</v>
       </c>
       <c r="M3" t="n">
-        <v>322154556.71</v>
+        <v>455120671.3</v>
       </c>
       <c r="N3" t="n">
-        <v>100710104.22</v>
+        <v>96921157.42</v>
       </c>
       <c r="O3" t="n">
-        <v>1616043872.855645</v>
+        <v>2454277832.637691</v>
       </c>
       <c r="P3" t="n">
-        <v>1517014757.66</v>
+        <v>1951844361.82</v>
       </c>
       <c r="Q3" t="n">
-        <v>24774106821.04</v>
+        <v>22618188703.55</v>
       </c>
       <c r="R3" t="n">
-        <v>17777698.17</v>
+        <v>14835407.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1908604025.69</v>
+        <v>2806101867.1</v>
       </c>
       <c r="T3" t="n">
-        <v>2050851369</v>
+        <v>2007244305</v>
       </c>
       <c r="U3" t="n">
-        <v>2050851369</v>
+        <v>2007244305</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7397</v>
+        <v>0.9724</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7397</v>
+        <v>0.9724</v>
       </c>
       <c r="X3" t="n">
-        <v>1517014757.66</v>
+        <v>1951844361.82</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1517014757.66</v>
+        <v>1951844361.82</v>
       </c>
       <c r="AA3" t="n">
-        <v>11608026.24</v>
+        <v>-20861009.33</v>
       </c>
       <c r="AB3" t="n">
-        <v>1505406731.42</v>
+        <v>1972705371.15</v>
       </c>
       <c r="AC3" t="n">
-        <v>1505406731.42</v>
+        <v>1972705371.15</v>
       </c>
       <c r="AD3" t="n">
-        <v>489825063.06</v>
+        <v>841093556.92</v>
       </c>
       <c r="AE3" t="n">
-        <v>1995231794.48</v>
+        <v>2813798928.07</v>
       </c>
       <c r="AF3" t="n">
-        <v>86627768.79000001</v>
+        <v>7697060.97</v>
       </c>
       <c r="AG3" t="n">
-        <v>-131250933.78</v>
+        <v>-721222814.26</v>
       </c>
       <c r="AH3" t="n">
-        <v>-21828043.97</v>
+        <v>-26925.76</v>
       </c>
       <c r="AI3" t="n">
-        <v>-42448282.42</v>
+        <v>66683505.74</v>
       </c>
       <c r="AJ3" t="n">
-        <v>195527260.17</v>
+        <v>654566234.28</v>
       </c>
       <c r="AK3" t="n">
-        <v>-242831762.26</v>
+        <v>-379720508.56</v>
       </c>
       <c r="AL3" t="n">
-        <v>21387309.77</v>
+        <v>21520994.68</v>
       </c>
       <c r="AM3" t="n">
-        <v>322154556.71</v>
+        <v>455120671.3</v>
       </c>
       <c r="AN3" t="n">
-        <v>100710104.22</v>
+        <v>96921157.42</v>
       </c>
       <c r="AO3" t="n">
-        <v>2225192391.95</v>
+        <v>3845805487.46</v>
       </c>
       <c r="AP3" t="n">
-        <v>1717265077.14</v>
+        <v>1540158470.47</v>
       </c>
       <c r="AQ3" t="n">
-        <v>256343397.63</v>
+        <v>348212300.48</v>
       </c>
       <c r="AR3" t="n">
-        <v>60118315.59</v>
+        <v>52741696.06</v>
       </c>
       <c r="AS3" t="n">
-        <v>34993683.01</v>
+        <v>39201384.53</v>
       </c>
       <c r="AT3" t="n">
-        <v>25124632.58</v>
+        <v>13540311.53</v>
       </c>
       <c r="AU3" t="n">
-        <v>745072886.08</v>
+        <v>526733196.3</v>
       </c>
       <c r="AV3" t="n">
-        <v>295536936.43</v>
+        <v>242349013.32</v>
       </c>
       <c r="AW3" t="n">
-        <v>213125259.17</v>
+        <v>165037868.85</v>
       </c>
       <c r="AX3" t="n">
-        <v>82411677.26000001</v>
+        <v>77311144.47</v>
       </c>
       <c r="AY3" t="n">
-        <v>17777698.17</v>
+        <v>14835407.18</v>
       </c>
       <c r="AZ3" t="n">
-        <v>3942457469.09</v>
+        <v>5385963957.93</v>
       </c>
       <c r="BA3" t="n">
-        <v>23056841743.9</v>
+        <v>21078030233.08</v>
       </c>
       <c r="BB3" t="n">
-        <v>26999299212.99</v>
+        <v>26463994191.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>26999299212.99</v>
+        <v>26463994191.01</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-214220309.462309</v>
+        <v>-32221818.584355</v>
       </c>
       <c r="C4" t="n">
-        <v>0.298917</v>
+        <v>0.245498</v>
       </c>
       <c r="D4" t="n">
-        <v>4340959626.73</v>
+        <v>2897104832.86</v>
       </c>
       <c r="E4" t="n">
-        <v>-716653780.28</v>
+        <v>-131250933.78</v>
       </c>
       <c r="F4" t="n">
-        <v>-716653780.28</v>
+        <v>-131250933.78</v>
       </c>
       <c r="G4" t="n">
-        <v>1951844361.82</v>
+        <v>1517014757.66</v>
       </c>
       <c r="H4" t="n">
-        <v>355386247.08</v>
+        <v>448467547.89</v>
       </c>
       <c r="I4" t="n">
-        <v>21078030233.08</v>
+        <v>23056841743.9</v>
       </c>
       <c r="J4" t="n">
-        <v>3624305846.45</v>
+        <v>2765853899.08</v>
       </c>
       <c r="K4" t="n">
-        <v>3268919599.37</v>
+        <v>2317386351.19</v>
       </c>
       <c r="L4" t="n">
-        <v>-379720508.56</v>
+        <v>-242831762.26</v>
       </c>
       <c r="M4" t="n">
-        <v>455120671.3</v>
+        <v>322154556.71</v>
       </c>
       <c r="N4" t="n">
-        <v>96921157.42</v>
+        <v>100710104.22</v>
       </c>
       <c r="O4" t="n">
-        <v>2454277832.637691</v>
+        <v>1616043872.855645</v>
       </c>
       <c r="P4" t="n">
-        <v>1951844361.82</v>
+        <v>1517014757.66</v>
       </c>
       <c r="Q4" t="n">
-        <v>22618188703.55</v>
+        <v>24774106821.04</v>
       </c>
       <c r="R4" t="n">
-        <v>14835407.18</v>
+        <v>17777698.17</v>
       </c>
       <c r="S4" t="n">
-        <v>2806101867.1</v>
+        <v>1908604025.69</v>
       </c>
       <c r="T4" t="n">
-        <v>2007244305</v>
+        <v>2050851369</v>
       </c>
       <c r="U4" t="n">
-        <v>2007244305</v>
+        <v>2050851369</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9724</v>
+        <v>0.7397</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9724</v>
+        <v>0.7397</v>
       </c>
       <c r="X4" t="n">
-        <v>1951844361.82</v>
+        <v>1517014757.66</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1951844361.82</v>
+        <v>1517014757.66</v>
       </c>
       <c r="AA4" t="n">
-        <v>-20861009.33</v>
+        <v>11608026.24</v>
       </c>
       <c r="AB4" t="n">
-        <v>1972705371.15</v>
+        <v>1505406731.42</v>
       </c>
       <c r="AC4" t="n">
-        <v>1972705371.15</v>
+        <v>1505406731.42</v>
       </c>
       <c r="AD4" t="n">
-        <v>841093556.92</v>
+        <v>489825063.06</v>
       </c>
       <c r="AE4" t="n">
-        <v>2813798928.07</v>
+        <v>1995231794.48</v>
       </c>
       <c r="AF4" t="n">
-        <v>7697060.97</v>
+        <v>86627768.79000001</v>
       </c>
       <c r="AG4" t="n">
-        <v>-721222814.26</v>
+        <v>-131250933.78</v>
       </c>
       <c r="AH4" t="n">
-        <v>-26925.76</v>
+        <v>-21828043.97</v>
       </c>
       <c r="AI4" t="n">
-        <v>66683505.74</v>
+        <v>-42448282.42</v>
       </c>
       <c r="AJ4" t="n">
-        <v>654566234.28</v>
+        <v>195527260.17</v>
       </c>
       <c r="AK4" t="n">
-        <v>-379720508.56</v>
+        <v>-242831762.26</v>
       </c>
       <c r="AL4" t="n">
-        <v>21520994.68</v>
+        <v>21387309.77</v>
       </c>
       <c r="AM4" t="n">
-        <v>455120671.3</v>
+        <v>322154556.71</v>
       </c>
       <c r="AN4" t="n">
-        <v>96921157.42</v>
+        <v>100710104.22</v>
       </c>
       <c r="AO4" t="n">
-        <v>3845805487.46</v>
+        <v>2225192391.95</v>
       </c>
       <c r="AP4" t="n">
-        <v>1540158470.47</v>
+        <v>1717265077.14</v>
       </c>
       <c r="AQ4" t="n">
-        <v>348212300.48</v>
+        <v>256343397.63</v>
       </c>
       <c r="AR4" t="n">
-        <v>52741696.06</v>
+        <v>60118315.59</v>
       </c>
       <c r="AS4" t="n">
-        <v>39201384.53</v>
+        <v>34993683.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>13540311.53</v>
+        <v>25124632.58</v>
       </c>
       <c r="AU4" t="n">
-        <v>526733196.3</v>
+        <v>745072886.08</v>
       </c>
       <c r="AV4" t="n">
-        <v>242349013.32</v>
+        <v>295536936.43</v>
       </c>
       <c r="AW4" t="n">
-        <v>165037868.85</v>
+        <v>213125259.17</v>
       </c>
       <c r="AX4" t="n">
-        <v>77311144.47</v>
+        <v>82411677.26000001</v>
       </c>
       <c r="AY4" t="n">
-        <v>14835407.18</v>
+        <v>17777698.17</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5385963957.93</v>
+        <v>3942457469.09</v>
       </c>
       <c r="BA4" t="n">
-        <v>21078030233.08</v>
+        <v>23056841743.9</v>
       </c>
       <c r="BB4" t="n">
-        <v>26463994191.01</v>
+        <v>26999299212.99</v>
       </c>
       <c r="BC4" t="n">
-        <v>26463994191.01</v>
+        <v>26999299212.99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-127679502.421345</v>
+        <v>-230373737.443557</v>
       </c>
       <c r="C5" t="n">
-        <v>0.297417</v>
+        <v>0.396582</v>
       </c>
       <c r="D5" t="n">
-        <v>3794332198.36</v>
+        <v>2255253542.32</v>
       </c>
       <c r="E5" t="n">
-        <v>-429294379.19</v>
+        <v>-580897483.71</v>
       </c>
       <c r="F5" t="n">
-        <v>-429294379.19</v>
+        <v>-580897483.71</v>
       </c>
       <c r="G5" t="n">
-        <v>1933357215.84</v>
+        <v>620571968.02</v>
       </c>
       <c r="H5" t="n">
-        <v>251694687.84</v>
+        <v>402276302.97</v>
       </c>
       <c r="I5" t="n">
-        <v>18675894353.81</v>
+        <v>17954869511.73</v>
       </c>
       <c r="J5" t="n">
-        <v>3365037819.17</v>
+        <v>1674356058.61</v>
       </c>
       <c r="K5" t="n">
-        <v>3113343131.33</v>
+        <v>1272079755.64</v>
       </c>
       <c r="L5" t="n">
-        <v>-257177261.08</v>
+        <v>-163606219.45</v>
       </c>
       <c r="M5" t="n">
-        <v>335521800.82</v>
+        <v>288344589.29</v>
       </c>
       <c r="N5" t="n">
-        <v>97463343.45999999</v>
+        <v>135529489.11</v>
       </c>
       <c r="O5" t="n">
-        <v>2234972092.608655</v>
+        <v>971095714.286443</v>
       </c>
       <c r="P5" t="n">
-        <v>1933357215.84</v>
+        <v>620571968.02</v>
       </c>
       <c r="Q5" t="n">
-        <v>19855560881.76</v>
-      </c>
-      <c r="R5" t="n">
-        <v>17738124.74</v>
-      </c>
+        <v>19660705793.47</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>2807736737.39</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2012655857</v>
-      </c>
+        <v>986690844.77</v>
+      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>2012655857</v>
+        <v>2371310539</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9606</v>
+        <v>0.2617</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9606</v>
+        <v>0.2617</v>
       </c>
       <c r="X5" t="n">
-        <v>1933357215.84</v>
+        <v>620571968.02</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1933357215.84</v>
+        <v>620571968.02</v>
       </c>
       <c r="AA5" t="n">
-        <v>-18292465.36</v>
+        <v>26968887.42</v>
       </c>
       <c r="AB5" t="n">
-        <v>1951649681.2</v>
+        <v>593603080.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>1951649681.2</v>
+        <v>593603080.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>826171649.3099999</v>
+        <v>390132085.75</v>
       </c>
       <c r="AE5" t="n">
-        <v>2777821330.51</v>
+        <v>983735166.35</v>
       </c>
       <c r="AF5" t="n">
-        <v>-29915406.88</v>
+        <v>-2955678.42</v>
       </c>
       <c r="AG5" t="n">
-        <v>-431343957.35</v>
-      </c>
-      <c r="AH5" t="inlineStr"/>
+        <v>-580897483.71</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-5755100.55</v>
+      </c>
       <c r="AI5" t="n">
-        <v>119127650.01</v>
+        <v>59967587.92</v>
       </c>
       <c r="AJ5" t="n">
-        <v>312216307.34</v>
+        <v>526684996.34</v>
       </c>
       <c r="AK5" t="n">
-        <v>-257177261.08</v>
+        <v>-163606219.45</v>
       </c>
       <c r="AL5" t="n">
-        <v>19118803.72</v>
+        <v>10791119.27</v>
       </c>
       <c r="AM5" t="n">
-        <v>335521800.82</v>
+        <v>288344589.29</v>
       </c>
       <c r="AN5" t="n">
-        <v>97463343.45999999</v>
+        <v>135529489.11</v>
       </c>
       <c r="AO5" t="n">
-        <v>3413770989.3</v>
+        <v>1696648465.19</v>
       </c>
       <c r="AP5" t="n">
-        <v>1179666527.95</v>
+        <v>1705836281.74</v>
       </c>
       <c r="AQ5" t="n">
-        <v>137684332.48</v>
+        <v>505451080.98</v>
       </c>
       <c r="AR5" t="n">
-        <v>33023077.17</v>
+        <v>81609075.92</v>
       </c>
       <c r="AS5" t="n">
-        <v>16873058.24</v>
+        <v>41674247.76</v>
       </c>
       <c r="AT5" t="n">
-        <v>16150018.93</v>
+        <v>39934828.16</v>
       </c>
       <c r="AU5" t="n">
-        <v>416461502.81</v>
+        <v>500641329.77</v>
       </c>
       <c r="AV5" t="n">
-        <v>295235866.93</v>
+        <v>330165878.32</v>
       </c>
       <c r="AW5" t="n">
-        <v>211986058.76</v>
+        <v>261830170.99</v>
       </c>
       <c r="AX5" t="n">
-        <v>83249808.17</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>17738124.74</v>
-      </c>
+        <v>68335707.33</v>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="n">
-        <v>4593437517.25</v>
+        <v>3402484746.93</v>
       </c>
       <c r="BA5" t="n">
-        <v>18675894353.81</v>
+        <v>17954869511.73</v>
       </c>
       <c r="BB5" t="n">
-        <v>23269331871.06</v>
+        <v>21357354258.66</v>
       </c>
       <c r="BC5" t="n">
-        <v>23269331871.06</v>
+        <v>21357354258.66</v>
       </c>
     </row>
   </sheetData>
@@ -1743,104 +1743,212 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46022</v>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="n">
-        <v>1551430584.13</v>
-      </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1868545434</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1868545434</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2777856968.11</v>
+      </c>
+      <c r="E2" t="n">
+        <v>14262410235.89</v>
+      </c>
+      <c r="F2" t="n">
+        <v>11582340739.2</v>
+      </c>
+      <c r="G2" t="n">
+        <v>23895496507.51</v>
+      </c>
+      <c r="H2" t="n">
+        <v>13912779834.49</v>
+      </c>
+      <c r="I2" t="n">
+        <v>11582340739.2</v>
+      </c>
+      <c r="J2" t="n">
+        <v>359509640.76</v>
+      </c>
+      <c r="K2" t="n">
+        <v>12705373539.78</v>
+      </c>
+      <c r="L2" t="n">
+        <v>22013368313.07</v>
+      </c>
+      <c r="M2" t="n">
+        <v>12826521167.42</v>
+      </c>
+      <c r="N2" t="n">
+        <v>121147627.64</v>
+      </c>
+      <c r="O2" t="n">
+        <v>12705373539.78</v>
+      </c>
+      <c r="P2" t="n">
+        <v>3196933962.26</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>4752176551.08</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>1868545434</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1868545434</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>46997495224.8</v>
+      </c>
+      <c r="W2" t="n">
+        <v>9887386437.43</v>
+      </c>
+      <c r="X2" t="n">
+        <v>27185889.77</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>11935831.45</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>6196185.9</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>174564116.26</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>9667504414.049999</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>359509640.76</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>9307994773.290001</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>37110108787.37</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>4006120386.83</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>4594905821.84</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1882128194.44</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>18109033505.52</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>2065658976</v>
+      </c>
       <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
+      <c r="AL2" t="n">
+        <v>1915000110.27</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>14128374419.25</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>59824016392.22</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>8801127770.360001</v>
+      </c>
       <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
-      <c r="BI2" t="inlineStr"/>
-      <c r="BJ2" t="inlineStr"/>
-      <c r="BK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>14703032970.36</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>23900997.3</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>22140699.88</v>
-      </c>
-      <c r="BO2" t="inlineStr"/>
-      <c r="BP2" t="inlineStr"/>
-      <c r="BQ2" t="n">
-        <v>-675620612.6799999</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>3910419162.8</v>
-      </c>
-      <c r="BS2" t="inlineStr"/>
-      <c r="BT2" t="inlineStr"/>
-      <c r="BU2" t="inlineStr"/>
-      <c r="BV2" t="n">
-        <v>393721123.03</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>8984296021.77</v>
-      </c>
+      <c r="AQ2" t="n">
+        <v>100931116.16</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>2455255505.34</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1039647542.45</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1039647542.45</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>115148282.5</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>3056967904.63</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1123032800.58</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1106542808.48</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>16489992.1</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>643489430.58</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>-565099313.59</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1208588744.17</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>12980465</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>300829222.22</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>619332713.59</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>275446343.36</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>51022888621.86</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>1671761934.49</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>212652673.33</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>28505118707.66</v>
+      </c>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="n">
+        <v>8840718462.969999</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>3368192447.87</v>
+      </c>
+      <c r="BQ2" t="inlineStr"/>
+      <c r="BR2" t="inlineStr"/>
+      <c r="BS2" t="n">
+        <v>8424444395.54</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>12178395.92</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>8412265999.62</v>
+      </c>
+      <c r="BV2" t="inlineStr"/>
+      <c r="BW2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45657</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>1868545434</v>
@@ -1849,49 +1957,49 @@
         <v>1868545434</v>
       </c>
       <c r="D3" t="n">
-        <v>1899776517.28</v>
+        <v>6363681531.23</v>
       </c>
       <c r="E3" t="n">
-        <v>16024197052.18</v>
+        <v>19175551810.85</v>
       </c>
       <c r="F3" t="n">
-        <v>13213675430.42</v>
+        <v>12107340342.65</v>
       </c>
       <c r="G3" t="n">
-        <v>26553122964.47</v>
+        <v>29295330536.2</v>
       </c>
       <c r="H3" t="n">
-        <v>16084945675.59</v>
+        <v>17593046632.05</v>
       </c>
       <c r="I3" t="n">
-        <v>13213675430.42</v>
+        <v>12107340342.65</v>
       </c>
       <c r="J3" t="n">
-        <v>214237409.34</v>
+        <v>332754449.88</v>
       </c>
       <c r="K3" t="n">
-        <v>14589498474.27</v>
+        <v>13713933024.62</v>
       </c>
       <c r="L3" t="n">
-        <v>26282422964.47</v>
+        <v>25274699964.96</v>
       </c>
       <c r="M3" t="n">
-        <v>15024698962.98</v>
+        <v>14087904410.34</v>
       </c>
       <c r="N3" t="n">
-        <v>435200488.71</v>
+        <v>373971385.72</v>
       </c>
       <c r="O3" t="n">
-        <v>14589498474.27</v>
+        <v>13713933024.62</v>
       </c>
       <c r="P3" t="n">
-        <v>3197216981.13</v>
+        <v>3196933962.26</v>
       </c>
       <c r="Q3" t="n">
-        <v>6756162329.39</v>
+        <v>5950156501.09</v>
       </c>
       <c r="R3" t="n">
-        <v>1548156957.65</v>
+        <v>1554847814.56</v>
       </c>
       <c r="S3" t="n">
         <v>1868545434</v>
@@ -1901,164 +2009,162 @@
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>48878170258.25</v>
+        <v>55210719735.72</v>
       </c>
       <c r="W3" t="n">
-        <v>12133187284.21</v>
+        <v>12118048982.88</v>
       </c>
       <c r="X3" t="n">
-        <v>15650212.1</v>
+        <v>5652665.63</v>
       </c>
       <c r="Y3" t="n">
-        <v>5712112.52</v>
+        <v>6571517.56</v>
       </c>
       <c r="Z3" t="n">
-        <v>41306023.2</v>
+        <v>5476240.41</v>
       </c>
       <c r="AA3" t="n">
-        <v>163357036.85</v>
+        <v>206827169.06</v>
       </c>
       <c r="AB3" t="n">
-        <v>11907161899.54</v>
+        <v>11893521390.22</v>
       </c>
       <c r="AC3" t="n">
-        <v>214237409.34</v>
+        <v>332754449.88</v>
       </c>
       <c r="AD3" t="n">
-        <v>11692924490.2</v>
+        <v>11560766940.34</v>
       </c>
       <c r="AE3" t="n">
-        <v>36744982974.04</v>
+        <v>43092670752.84</v>
       </c>
       <c r="AF3" t="n">
-        <v>2579129406.01</v>
+        <v>3524962283.14</v>
       </c>
       <c r="AG3" t="n">
-        <v>4117035152.64</v>
+        <v>7282030420.63</v>
       </c>
       <c r="AH3" t="n">
-        <v>270700000</v>
+        <v>4020630571.24</v>
       </c>
       <c r="AI3" t="n">
-        <v>21174190387</v>
+        <v>22599506152.34</v>
       </c>
       <c r="AJ3" t="n">
-        <v>3107111861.12</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>19340.5</v>
-      </c>
+        <v>2701134121.33</v>
+      </c>
+      <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>965270132.45</v>
+        <v>1116115916.5</v>
       </c>
       <c r="AM3" t="n">
-        <v>17101789052.93</v>
+        <v>18782256114.51</v>
       </c>
       <c r="AN3" t="n">
-        <v>63902869221.23</v>
+        <v>69298624146.06</v>
       </c>
       <c r="AO3" t="n">
-        <v>11072940571.6</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>2917089983.18</v>
-      </c>
+        <v>8612906761.17</v>
+      </c>
+      <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="n">
-        <v>167833564.68</v>
+        <v>172914342.78</v>
       </c>
       <c r="AR3" t="n">
-        <v>1698064039.4</v>
+        <v>1888209868.14</v>
       </c>
       <c r="AS3" t="n">
-        <v>920997756.55</v>
+        <v>788836515.36</v>
       </c>
       <c r="AT3" t="n">
-        <v>920997756.55</v>
+        <v>788836515.36</v>
       </c>
       <c r="AU3" t="n">
-        <v>199441821.69</v>
+        <v>144342080.45</v>
       </c>
       <c r="AV3" t="n">
-        <v>2873650869.86</v>
+        <v>3122459589.3</v>
       </c>
       <c r="AW3" t="n">
-        <v>1375823043.85</v>
+        <v>1606592681.97</v>
       </c>
       <c r="AX3" t="n">
-        <v>1325013445.55</v>
+        <v>1587142131.23</v>
       </c>
       <c r="AY3" t="n">
-        <v>50809598.3</v>
+        <v>19450550.74</v>
       </c>
       <c r="AZ3" t="n">
-        <v>722221974.0599999</v>
+        <v>642775049.1799999</v>
       </c>
       <c r="BA3" t="n">
-        <v>-920150157.9</v>
+        <v>-670620339.12</v>
       </c>
       <c r="BB3" t="n">
-        <v>1642372131.96</v>
+        <v>1313395388.3</v>
       </c>
       <c r="BC3" t="n">
-        <v>18196893.77</v>
+        <v>34955705.64</v>
       </c>
       <c r="BD3" t="n">
-        <v>300549532.68</v>
+        <v>309358314.21</v>
       </c>
       <c r="BE3" t="n">
-        <v>706092288.36</v>
+        <v>708082129.86</v>
       </c>
       <c r="BF3" t="n">
-        <v>617533417.15</v>
+        <v>260999238.59</v>
       </c>
       <c r="BG3" t="n">
-        <v>52829928649.63</v>
+        <v>60685717384.89</v>
       </c>
       <c r="BH3" t="n">
-        <v>1452138757.46</v>
+        <v>980251720.15</v>
       </c>
       <c r="BI3" t="n">
-        <v>226724114.32</v>
+        <v>267659472.47</v>
       </c>
       <c r="BJ3" t="n">
-        <v>23257598557.29</v>
+        <v>32828474304.83</v>
       </c>
       <c r="BK3" t="n">
         <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>23217116166.19</v>
+        <v>32742836184.17</v>
       </c>
       <c r="BM3" t="n">
-        <v>20361788.86</v>
+        <v>65647032.79</v>
       </c>
       <c r="BN3" t="n">
-        <v>20120602.24</v>
+        <v>19991087.87</v>
       </c>
       <c r="BO3" t="n">
-        <v>14488618599.08</v>
+        <v>14182056105.18</v>
       </c>
       <c r="BP3" t="n">
-        <v>3341000648.56</v>
+        <v>3176312372.01</v>
       </c>
       <c r="BQ3" t="n">
-        <v>-674230825.62</v>
+        <v>-578329425.16</v>
       </c>
       <c r="BR3" t="n">
-        <v>4015231474.18</v>
+        <v>3754641797.17</v>
       </c>
       <c r="BS3" t="n">
-        <v>10063847972.92</v>
-      </c>
-      <c r="BT3" t="inlineStr"/>
+        <v>9250963410.25</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>33247429.9</v>
+      </c>
       <c r="BU3" t="n">
-        <v>10063847972.92</v>
+        <v>9217715980.35</v>
       </c>
       <c r="BV3" t="n">
-        <v>46686812.17</v>
+        <v>120430891.62</v>
       </c>
       <c r="BW3" t="n">
-        <v>10017161160.75</v>
+        <v>9097285088.73</v>
       </c>
     </row>
     <row r="4">
@@ -2286,7 +2392,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44926</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>1868545434</v>
@@ -2295,49 +2401,49 @@
         <v>1868545434</v>
       </c>
       <c r="D5" t="n">
-        <v>6363681531.23</v>
+        <v>1899776517.28</v>
       </c>
       <c r="E5" t="n">
-        <v>19175551810.85</v>
+        <v>16024197052.18</v>
       </c>
       <c r="F5" t="n">
-        <v>12107340342.65</v>
+        <v>13213675430.42</v>
       </c>
       <c r="G5" t="n">
-        <v>29295330536.2</v>
+        <v>26553122964.47</v>
       </c>
       <c r="H5" t="n">
-        <v>17593046632.05</v>
+        <v>16084945675.59</v>
       </c>
       <c r="I5" t="n">
-        <v>12107340342.65</v>
+        <v>13213675430.42</v>
       </c>
       <c r="J5" t="n">
-        <v>332754449.88</v>
+        <v>214237409.34</v>
       </c>
       <c r="K5" t="n">
-        <v>13713933024.62</v>
+        <v>14589498474.27</v>
       </c>
       <c r="L5" t="n">
-        <v>25274699964.96</v>
+        <v>26282422964.47</v>
       </c>
       <c r="M5" t="n">
-        <v>14087904410.34</v>
+        <v>15024698962.98</v>
       </c>
       <c r="N5" t="n">
-        <v>373971385.72</v>
+        <v>435200488.71</v>
       </c>
       <c r="O5" t="n">
-        <v>13713933024.62</v>
+        <v>14589498474.27</v>
       </c>
       <c r="P5" t="n">
-        <v>3196933962.26</v>
+        <v>3197216981.13</v>
       </c>
       <c r="Q5" t="n">
-        <v>5950156501.09</v>
+        <v>6756162329.39</v>
       </c>
       <c r="R5" t="n">
-        <v>1554847814.56</v>
+        <v>1548156957.65</v>
       </c>
       <c r="S5" t="n">
         <v>1868545434</v>
@@ -2347,368 +2453,262 @@
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>55210719735.72</v>
+        <v>48878170258.25</v>
       </c>
       <c r="W5" t="n">
-        <v>12118048982.88</v>
+        <v>12133187284.21</v>
       </c>
       <c r="X5" t="n">
-        <v>5652665.63</v>
+        <v>15650212.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>6571517.56</v>
+        <v>5712112.52</v>
       </c>
       <c r="Z5" t="n">
-        <v>5476240.41</v>
+        <v>41306023.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>206827169.06</v>
+        <v>163357036.85</v>
       </c>
       <c r="AB5" t="n">
-        <v>11893521390.22</v>
+        <v>11907161899.54</v>
       </c>
       <c r="AC5" t="n">
-        <v>332754449.88</v>
+        <v>214237409.34</v>
       </c>
       <c r="AD5" t="n">
-        <v>11560766940.34</v>
+        <v>11692924490.2</v>
       </c>
       <c r="AE5" t="n">
-        <v>43092670752.84</v>
+        <v>36744982974.04</v>
       </c>
       <c r="AF5" t="n">
-        <v>3524962283.14</v>
+        <v>2579129406.01</v>
       </c>
       <c r="AG5" t="n">
-        <v>7282030420.63</v>
+        <v>4117035152.64</v>
       </c>
       <c r="AH5" t="n">
-        <v>4020630571.24</v>
+        <v>270700000</v>
       </c>
       <c r="AI5" t="n">
-        <v>22599506152.34</v>
+        <v>21174190387</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2701134121.33</v>
-      </c>
-      <c r="AK5" t="inlineStr"/>
+        <v>3107111861.12</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>19340.5</v>
+      </c>
       <c r="AL5" t="n">
-        <v>1116115916.5</v>
+        <v>965270132.45</v>
       </c>
       <c r="AM5" t="n">
-        <v>18782256114.51</v>
+        <v>17101789052.93</v>
       </c>
       <c r="AN5" t="n">
-        <v>69298624146.06</v>
+        <v>63902869221.23</v>
       </c>
       <c r="AO5" t="n">
-        <v>8612906761.17</v>
-      </c>
-      <c r="AP5" t="inlineStr"/>
+        <v>11072940571.6</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>2917089983.18</v>
+      </c>
       <c r="AQ5" t="n">
-        <v>172914342.78</v>
+        <v>167833564.68</v>
       </c>
       <c r="AR5" t="n">
-        <v>1888209868.14</v>
+        <v>1698064039.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>788836515.36</v>
+        <v>920997756.55</v>
       </c>
       <c r="AT5" t="n">
-        <v>788836515.36</v>
+        <v>920997756.55</v>
       </c>
       <c r="AU5" t="n">
-        <v>144342080.45</v>
+        <v>199441821.69</v>
       </c>
       <c r="AV5" t="n">
-        <v>3122459589.3</v>
+        <v>2873650869.86</v>
       </c>
       <c r="AW5" t="n">
-        <v>1606592681.97</v>
+        <v>1375823043.85</v>
       </c>
       <c r="AX5" t="n">
-        <v>1587142131.23</v>
+        <v>1325013445.55</v>
       </c>
       <c r="AY5" t="n">
-        <v>19450550.74</v>
+        <v>50809598.3</v>
       </c>
       <c r="AZ5" t="n">
-        <v>642775049.1799999</v>
+        <v>722221974.0599999</v>
       </c>
       <c r="BA5" t="n">
-        <v>-670620339.12</v>
+        <v>-920150157.9</v>
       </c>
       <c r="BB5" t="n">
-        <v>1313395388.3</v>
+        <v>1642372131.96</v>
       </c>
       <c r="BC5" t="n">
-        <v>34955705.64</v>
+        <v>18196893.77</v>
       </c>
       <c r="BD5" t="n">
-        <v>309358314.21</v>
+        <v>300549532.68</v>
       </c>
       <c r="BE5" t="n">
-        <v>708082129.86</v>
+        <v>706092288.36</v>
       </c>
       <c r="BF5" t="n">
-        <v>260999238.59</v>
+        <v>617533417.15</v>
       </c>
       <c r="BG5" t="n">
-        <v>60685717384.89</v>
+        <v>52829928649.63</v>
       </c>
       <c r="BH5" t="n">
-        <v>980251720.15</v>
+        <v>1452138757.46</v>
       </c>
       <c r="BI5" t="n">
-        <v>267659472.47</v>
+        <v>226724114.32</v>
       </c>
       <c r="BJ5" t="n">
-        <v>32828474304.83</v>
+        <v>23257598557.29</v>
       </c>
       <c r="BK5" t="n">
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>32742836184.17</v>
+        <v>23217116166.19</v>
       </c>
       <c r="BM5" t="n">
-        <v>65647032.79</v>
+        <v>20361788.86</v>
       </c>
       <c r="BN5" t="n">
-        <v>19991087.87</v>
+        <v>20120602.24</v>
       </c>
       <c r="BO5" t="n">
-        <v>14182056105.18</v>
+        <v>14488618599.08</v>
       </c>
       <c r="BP5" t="n">
-        <v>3176312372.01</v>
+        <v>3341000648.56</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-578329425.16</v>
+        <v>-674230825.62</v>
       </c>
       <c r="BR5" t="n">
-        <v>3754641797.17</v>
+        <v>4015231474.18</v>
       </c>
       <c r="BS5" t="n">
-        <v>9250963410.25</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>33247429.9</v>
-      </c>
+        <v>10063847972.92</v>
+      </c>
+      <c r="BT5" t="inlineStr"/>
       <c r="BU5" t="n">
-        <v>9217715980.35</v>
+        <v>10063847972.92</v>
       </c>
       <c r="BV5" t="n">
-        <v>120430891.62</v>
+        <v>46686812.17</v>
       </c>
       <c r="BW5" t="n">
-        <v>9097285088.73</v>
+        <v>10017161160.75</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>44561</v>
-      </c>
-      <c r="B6" t="n">
-        <v>1868545434</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1868545434</v>
-      </c>
-      <c r="D6" t="n">
-        <v>2777856968.11</v>
-      </c>
-      <c r="E6" t="n">
-        <v>14262410235.89</v>
-      </c>
-      <c r="F6" t="n">
-        <v>11582340739.2</v>
-      </c>
-      <c r="G6" t="n">
-        <v>23895496507.51</v>
-      </c>
-      <c r="H6" t="n">
-        <v>13912779834.49</v>
-      </c>
-      <c r="I6" t="n">
-        <v>11582340739.2</v>
-      </c>
-      <c r="J6" t="n">
-        <v>359509640.76</v>
-      </c>
-      <c r="K6" t="n">
-        <v>12705373539.78</v>
-      </c>
-      <c r="L6" t="n">
-        <v>22013368313.07</v>
-      </c>
-      <c r="M6" t="n">
-        <v>12826521167.42</v>
-      </c>
-      <c r="N6" t="n">
-        <v>121147627.64</v>
-      </c>
-      <c r="O6" t="n">
-        <v>12705373539.78</v>
-      </c>
-      <c r="P6" t="n">
-        <v>3196933962.26</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>4752176551.08</v>
-      </c>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="n">
-        <v>1868545434</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1868545434</v>
-      </c>
-      <c r="U6" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="n">
+        <v>1551430584.13</v>
+      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="n">
         <v>0</v>
       </c>
-      <c r="V6" t="n">
-        <v>46997495224.8</v>
-      </c>
-      <c r="W6" t="n">
-        <v>9887386437.43</v>
-      </c>
-      <c r="X6" t="n">
-        <v>27185889.77</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>11935831.45</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>6196185.9</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>174564116.26</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>9667504414.049999</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>359509640.76</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>9307994773.290001</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>37110108787.37</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>4006120386.83</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>4594905821.84</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1882128194.44</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>18109033505.52</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>2065658976</v>
-      </c>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="n">
-        <v>1915000110.27</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>14128374419.25</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>59824016392.22</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>8801127770.360001</v>
-      </c>
-      <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="n">
-        <v>100931116.16</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>2455255505.34</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>1039647542.45</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>1039647542.45</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>115148282.5</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>3056967904.63</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1123032800.58</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1106542808.48</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>16489992.1</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>643489430.58</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>-565099313.59</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1208588744.17</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>12980465</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>300829222.22</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>619332713.59</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>275446343.36</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>51022888621.86</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>1671761934.49</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>212652673.33</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>28505118707.66</v>
-      </c>
-      <c r="BK6" t="inlineStr"/>
-      <c r="BL6" t="inlineStr"/>
-      <c r="BM6" t="inlineStr"/>
-      <c r="BN6" t="inlineStr"/>
-      <c r="BO6" t="n">
-        <v>8840718462.969999</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>3368192447.87</v>
-      </c>
-      <c r="BQ6" t="inlineStr"/>
-      <c r="BR6" t="inlineStr"/>
-      <c r="BS6" t="n">
-        <v>8424444395.54</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>12178395.92</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>8412265999.62</v>
-      </c>
-      <c r="BV6" t="inlineStr"/>
-      <c r="BW6" t="inlineStr"/>
+      <c r="BL6" t="n">
+        <v>14703032970.36</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>23900997.3</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>22140699.88</v>
+      </c>
+      <c r="BO6" t="inlineStr"/>
+      <c r="BP6" t="inlineStr"/>
+      <c r="BQ6" t="n">
+        <v>-675620612.6799999</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>3910419162.8</v>
+      </c>
+      <c r="BS6" t="inlineStr"/>
+      <c r="BT6" t="inlineStr"/>
+      <c r="BU6" t="inlineStr"/>
+      <c r="BV6" t="n">
+        <v>393721123.03</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>8984296021.77</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2963,566 +2963,566 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>994840949.17</v>
+        <v>392169898.26</v>
       </c>
       <c r="C2" t="n">
-        <v>-12429718956.27</v>
+        <v>-31062665023.2</v>
       </c>
       <c r="D2" t="n">
-        <v>12059115525.64</v>
+        <v>30870707134.21</v>
       </c>
       <c r="E2" t="n">
-        <v>-145396995.68</v>
+        <v>-679824339.33</v>
       </c>
       <c r="F2" t="n">
-        <v>10017161160.75</v>
+        <v>7811060111.62</v>
       </c>
       <c r="G2" t="n">
-        <v>10646545468.83</v>
+        <v>8279324240.99</v>
       </c>
       <c r="H2" t="n">
-        <v>-629384308.08</v>
+        <v>-468264129.37</v>
       </c>
       <c r="I2" t="n">
-        <v>-1553199889.12</v>
+        <v>-1077552801.41</v>
       </c>
       <c r="J2" t="n">
-        <v>-20832604.45</v>
+        <v>664405579.8099999</v>
       </c>
       <c r="K2" t="n">
-        <v>-1161763854.04</v>
+        <v>-1550000492.23</v>
       </c>
       <c r="L2" t="n">
-        <v>-370603430.63</v>
+        <v>-191957888.99</v>
       </c>
       <c r="M2" t="n">
-        <v>-370603430.63</v>
+        <v>-191957888.99</v>
       </c>
       <c r="N2" t="n">
-        <v>-12429718956.27</v>
+        <v>-31062665023.2</v>
       </c>
       <c r="O2" t="n">
-        <v>12059115525.64</v>
+        <v>30870707134.21</v>
       </c>
       <c r="P2" t="n">
-        <v>-216422363.81</v>
+        <v>-462705565.55</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>-71320307.79000001</v>
+        <v>167846768.17</v>
       </c>
       <c r="S2" t="n">
-        <v>151179692.21</v>
+        <v>572746768.17</v>
       </c>
       <c r="T2" t="n">
-        <v>-222500000</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+        <v>-404900000</v>
+      </c>
+      <c r="U2" t="n">
+        <v>41354261.02</v>
+      </c>
+      <c r="V2" t="n">
+        <v>41354261.02</v>
+      </c>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="n">
-        <v>-145102056.02</v>
+        <v>-671906594.74</v>
       </c>
       <c r="Y2" t="n">
-        <v>294939.66</v>
+        <v>7917744.59</v>
       </c>
       <c r="Z2" t="n">
-        <v>-145396995.68</v>
+        <v>-679824339.33</v>
       </c>
       <c r="AA2" t="n">
-        <v>1140237944.85</v>
+        <v>1071994237.59</v>
       </c>
       <c r="AB2" t="n">
-        <v>-752799571.33</v>
+        <v>-1887005458.31</v>
       </c>
       <c r="AC2" t="n">
-        <v>75418380.47</v>
+        <v>-2138124396.64</v>
       </c>
       <c r="AD2" t="n">
-        <v>-3691678548.76</v>
+        <v>9502547861.6</v>
       </c>
       <c r="AE2" t="n">
-        <v>3189004381.3</v>
+        <v>-2269833695.99</v>
       </c>
       <c r="AF2" t="n">
-        <v>-325543784.34</v>
+        <v>-6981595227.28</v>
       </c>
       <c r="AG2" t="n">
-        <v>350491504.01</v>
+        <v>378559075.93</v>
       </c>
       <c r="AH2" t="n">
-        <v>402276302.97</v>
+        <v>251694687.84</v>
       </c>
       <c r="AI2" t="n">
-        <v>140920294.94</v>
+        <v>19282738.73</v>
       </c>
       <c r="AJ2" t="n">
-        <v>261356008.03</v>
+        <v>232411949.11</v>
       </c>
       <c r="AK2" t="n">
-        <v>-34213194.45</v>
+        <v>-46120214.16</v>
       </c>
       <c r="AL2" t="n">
-        <v>-5772761.21</v>
+        <v>-5550839.46</v>
       </c>
       <c r="AM2" t="n">
-        <v>593603080.6</v>
+        <v>1951649681.2</v>
       </c>
       <c r="AN2" t="n">
-        <v>1140237944.85</v>
+        <v>1071994237.59</v>
       </c>
       <c r="AO2" t="n">
-        <v>-1271256502.29</v>
+        <v>-5335021957.08</v>
       </c>
       <c r="AP2" t="n">
-        <v>-19582015160.72</v>
+        <v>-20678894982.29</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-1318213065.75</v>
+        <v>-881109128.53</v>
       </c>
       <c r="AR2" t="n">
-        <v>-2166407604.2</v>
+        <v>-1890420022.1</v>
       </c>
       <c r="AS2" t="n">
-        <v>-16097394490.77</v>
+        <v>-17907365831.66</v>
       </c>
       <c r="AT2" t="n">
-        <v>21993509607.86</v>
+        <v>27085911176.96</v>
       </c>
       <c r="AU2" t="n">
-        <v>244242904.03</v>
+        <v>305625165.99</v>
       </c>
       <c r="AV2" t="n">
-        <v>21749266703.83</v>
+        <v>26780286010.97</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>7017217409.6</v>
+        <v>-2170531574.48</v>
       </c>
       <c r="C3" t="n">
-        <v>-13053600000</v>
+        <v>-14391975000</v>
       </c>
       <c r="D3" t="n">
-        <v>9534550512.91</v>
+        <v>18819677895.87</v>
       </c>
       <c r="E3" t="n">
-        <v>-80009052.86</v>
+        <v>-715934267.54</v>
       </c>
       <c r="F3" t="n">
-        <v>10646545468.83</v>
+        <v>9097285088.73</v>
       </c>
       <c r="G3" t="n">
-        <v>9097285088.73</v>
+        <v>7811060111.62</v>
       </c>
       <c r="H3" t="n">
-        <v>1549260380.1</v>
+        <v>1286224977.11</v>
       </c>
       <c r="I3" t="n">
-        <v>-5055338288.14</v>
+        <v>3657122436.74</v>
       </c>
       <c r="J3" t="n">
-        <v>-58923547.95</v>
+        <v>819753738.4299999</v>
       </c>
       <c r="K3" t="n">
-        <v>-1458483362.37</v>
+        <v>-1576850159.26</v>
       </c>
       <c r="L3" t="n">
-        <v>-3519049487.09</v>
+        <v>4427702895.87</v>
       </c>
       <c r="M3" t="n">
-        <v>-3519049487.09</v>
+        <v>4427702895.87</v>
       </c>
       <c r="N3" t="n">
-        <v>-13053600000</v>
+        <v>-14391975000</v>
       </c>
       <c r="O3" t="n">
-        <v>9534550512.91</v>
+        <v>18819677895.87</v>
       </c>
       <c r="P3" t="n">
-        <v>-492627794.22</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>-504375000</v>
-      </c>
+        <v>-916300152.6900001</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>37706322.81</v>
+        <v>5208803.01</v>
       </c>
       <c r="S3" t="n">
-        <v>37706322.81</v>
-      </c>
-      <c r="T3" t="inlineStr"/>
+        <v>34108803.01</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-28900000</v>
+      </c>
       <c r="U3" t="n">
-        <v>-44932879.97</v>
+        <v>-205723729.94</v>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>-44932879.97</v>
+        <v>-205723729.94</v>
       </c>
       <c r="X3" t="n">
-        <v>18973762.94</v>
+        <v>-715785225.76</v>
       </c>
       <c r="Y3" t="n">
-        <v>98982815.8</v>
+        <v>149041.78</v>
       </c>
       <c r="Z3" t="n">
-        <v>-80009052.86</v>
+        <v>-715934267.54</v>
       </c>
       <c r="AA3" t="n">
-        <v>7097226462.46</v>
+        <v>-1454597306.94</v>
       </c>
       <c r="AB3" t="n">
-        <v>4690577929.21</v>
+        <v>-4954593060.43</v>
       </c>
       <c r="AC3" t="n">
-        <v>30420696.99</v>
+        <v>657923154.22</v>
       </c>
       <c r="AD3" t="n">
-        <v>577342908.55</v>
+        <v>2792769044.06</v>
       </c>
       <c r="AE3" t="n">
-        <v>5853250880.12</v>
+        <v>-4410436324.09</v>
       </c>
       <c r="AF3" t="n">
-        <v>-1770436556.45</v>
+        <v>-3994848934.62</v>
       </c>
       <c r="AG3" t="n">
-        <v>376066710.11</v>
+        <v>510030010.11</v>
       </c>
       <c r="AH3" t="n">
-        <v>448467547.89</v>
+        <v>355386247.08</v>
       </c>
       <c r="AI3" t="n">
-        <v>118698667.57</v>
+        <v>28991564.45</v>
       </c>
       <c r="AJ3" t="n">
-        <v>329768880.32</v>
+        <v>326394682.63</v>
       </c>
       <c r="AK3" t="n">
-        <v>-57151411.27</v>
+        <v>-59431634.92</v>
       </c>
       <c r="AL3" t="n">
-        <v>-19220022.65</v>
+        <v>56020.05</v>
       </c>
       <c r="AM3" t="n">
-        <v>1505406731.42</v>
+        <v>1972705371.15</v>
       </c>
       <c r="AN3" t="n">
-        <v>7097226462.46</v>
+        <v>-1454597306.94</v>
       </c>
       <c r="AO3" t="n">
-        <v>-2017045582.84</v>
+        <v>-1744994119.34</v>
       </c>
       <c r="AP3" t="n">
-        <v>-20050959543.34</v>
+        <v>-23331931411.84</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-682090342.5599999</v>
+        <v>-829690252.1799999</v>
       </c>
       <c r="AR3" t="n">
-        <v>-2795208651.3</v>
+        <v>-2376620939.04</v>
       </c>
       <c r="AS3" t="n">
-        <v>-16573660549.48</v>
+        <v>-20125620220.62</v>
       </c>
       <c r="AT3" t="n">
-        <v>29165231588.64</v>
+        <v>23622328224.24</v>
       </c>
       <c r="AU3" t="n">
-        <v>390988406.56</v>
+        <v>935637594.65</v>
       </c>
       <c r="AV3" t="n">
-        <v>28774243182.08</v>
+        <v>22686690629.59</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-2170531574.48</v>
+        <v>7017217409.6</v>
       </c>
       <c r="C4" t="n">
-        <v>-14391975000</v>
+        <v>-13053600000</v>
       </c>
       <c r="D4" t="n">
-        <v>18819677895.87</v>
+        <v>9534550512.91</v>
       </c>
       <c r="E4" t="n">
-        <v>-715934267.54</v>
+        <v>-80009052.86</v>
       </c>
       <c r="F4" t="n">
+        <v>10646545468.83</v>
+      </c>
+      <c r="G4" t="n">
         <v>9097285088.73</v>
       </c>
-      <c r="G4" t="n">
-        <v>7811060111.62</v>
-      </c>
       <c r="H4" t="n">
-        <v>1286224977.11</v>
+        <v>1549260380.1</v>
       </c>
       <c r="I4" t="n">
-        <v>3657122436.74</v>
+        <v>-5055338288.14</v>
       </c>
       <c r="J4" t="n">
-        <v>819753738.4299999</v>
+        <v>-58923547.95</v>
       </c>
       <c r="K4" t="n">
-        <v>-1576850159.26</v>
+        <v>-1458483362.37</v>
       </c>
       <c r="L4" t="n">
-        <v>4427702895.87</v>
+        <v>-3519049487.09</v>
       </c>
       <c r="M4" t="n">
-        <v>4427702895.87</v>
+        <v>-3519049487.09</v>
       </c>
       <c r="N4" t="n">
-        <v>-14391975000</v>
+        <v>-13053600000</v>
       </c>
       <c r="O4" t="n">
-        <v>18819677895.87</v>
+        <v>9534550512.91</v>
       </c>
       <c r="P4" t="n">
-        <v>-916300152.6900001</v>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+        <v>-492627794.22</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-504375000</v>
+      </c>
       <c r="R4" t="n">
-        <v>5208803.01</v>
+        <v>37706322.81</v>
       </c>
       <c r="S4" t="n">
-        <v>34108803.01</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-28900000</v>
-      </c>
+        <v>37706322.81</v>
+      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="n">
-        <v>-205723729.94</v>
+        <v>-44932879.97</v>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>-205723729.94</v>
+        <v>-44932879.97</v>
       </c>
       <c r="X4" t="n">
-        <v>-715785225.76</v>
+        <v>18973762.94</v>
       </c>
       <c r="Y4" t="n">
-        <v>149041.78</v>
+        <v>98982815.8</v>
       </c>
       <c r="Z4" t="n">
-        <v>-715934267.54</v>
+        <v>-80009052.86</v>
       </c>
       <c r="AA4" t="n">
-        <v>-1454597306.94</v>
+        <v>7097226462.46</v>
       </c>
       <c r="AB4" t="n">
-        <v>-4954593060.43</v>
+        <v>4690577929.21</v>
       </c>
       <c r="AC4" t="n">
-        <v>657923154.22</v>
+        <v>30420696.99</v>
       </c>
       <c r="AD4" t="n">
-        <v>2792769044.06</v>
+        <v>577342908.55</v>
       </c>
       <c r="AE4" t="n">
-        <v>-4410436324.09</v>
+        <v>5853250880.12</v>
       </c>
       <c r="AF4" t="n">
-        <v>-3994848934.62</v>
+        <v>-1770436556.45</v>
       </c>
       <c r="AG4" t="n">
-        <v>510030010.11</v>
+        <v>376066710.11</v>
       </c>
       <c r="AH4" t="n">
-        <v>355386247.08</v>
+        <v>448467547.89</v>
       </c>
       <c r="AI4" t="n">
-        <v>28991564.45</v>
+        <v>118698667.57</v>
       </c>
       <c r="AJ4" t="n">
-        <v>326394682.63</v>
+        <v>329768880.32</v>
       </c>
       <c r="AK4" t="n">
-        <v>-59431634.92</v>
+        <v>-57151411.27</v>
       </c>
       <c r="AL4" t="n">
-        <v>56020.05</v>
+        <v>-19220022.65</v>
       </c>
       <c r="AM4" t="n">
-        <v>1972705371.15</v>
+        <v>1505406731.42</v>
       </c>
       <c r="AN4" t="n">
-        <v>-1454597306.94</v>
+        <v>7097226462.46</v>
       </c>
       <c r="AO4" t="n">
-        <v>-1744994119.34</v>
+        <v>-2017045582.84</v>
       </c>
       <c r="AP4" t="n">
-        <v>-23331931411.84</v>
+        <v>-20050959543.34</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-829690252.1799999</v>
+        <v>-682090342.5599999</v>
       </c>
       <c r="AR4" t="n">
-        <v>-2376620939.04</v>
+        <v>-2795208651.3</v>
       </c>
       <c r="AS4" t="n">
-        <v>-20125620220.62</v>
+        <v>-16573660549.48</v>
       </c>
       <c r="AT4" t="n">
-        <v>23622328224.24</v>
+        <v>29165231588.64</v>
       </c>
       <c r="AU4" t="n">
-        <v>935637594.65</v>
+        <v>390988406.56</v>
       </c>
       <c r="AV4" t="n">
-        <v>22686690629.59</v>
+        <v>28774243182.08</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>392169898.26</v>
+        <v>994840949.17</v>
       </c>
       <c r="C5" t="n">
-        <v>-31062665023.2</v>
+        <v>-12429718956.27</v>
       </c>
       <c r="D5" t="n">
-        <v>30870707134.21</v>
+        <v>12059115525.64</v>
       </c>
       <c r="E5" t="n">
-        <v>-679824339.33</v>
+        <v>-145396995.68</v>
       </c>
       <c r="F5" t="n">
-        <v>7811060111.62</v>
+        <v>10017161160.75</v>
       </c>
       <c r="G5" t="n">
-        <v>8279324240.99</v>
+        <v>10646545468.83</v>
       </c>
       <c r="H5" t="n">
-        <v>-468264129.37</v>
+        <v>-629384308.08</v>
       </c>
       <c r="I5" t="n">
-        <v>-1077552801.41</v>
+        <v>-1553199889.12</v>
       </c>
       <c r="J5" t="n">
-        <v>664405579.8099999</v>
+        <v>-20832604.45</v>
       </c>
       <c r="K5" t="n">
-        <v>-1550000492.23</v>
+        <v>-1161763854.04</v>
       </c>
       <c r="L5" t="n">
-        <v>-191957888.99</v>
+        <v>-370603430.63</v>
       </c>
       <c r="M5" t="n">
-        <v>-191957888.99</v>
+        <v>-370603430.63</v>
       </c>
       <c r="N5" t="n">
-        <v>-31062665023.2</v>
+        <v>-12429718956.27</v>
       </c>
       <c r="O5" t="n">
-        <v>30870707134.21</v>
+        <v>12059115525.64</v>
       </c>
       <c r="P5" t="n">
-        <v>-462705565.55</v>
+        <v>-216422363.81</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>167846768.17</v>
+        <v>-71320307.79000001</v>
       </c>
       <c r="S5" t="n">
-        <v>572746768.17</v>
+        <v>151179692.21</v>
       </c>
       <c r="T5" t="n">
-        <v>-404900000</v>
-      </c>
-      <c r="U5" t="n">
-        <v>41354261.02</v>
-      </c>
-      <c r="V5" t="n">
-        <v>41354261.02</v>
-      </c>
+        <v>-222500000</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>-671906594.74</v>
+        <v>-145102056.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>7917744.59</v>
+        <v>294939.66</v>
       </c>
       <c r="Z5" t="n">
-        <v>-679824339.33</v>
+        <v>-145396995.68</v>
       </c>
       <c r="AA5" t="n">
-        <v>1071994237.59</v>
+        <v>1140237944.85</v>
       </c>
       <c r="AB5" t="n">
-        <v>-1887005458.31</v>
+        <v>-752799571.33</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2138124396.64</v>
+        <v>75418380.47</v>
       </c>
       <c r="AD5" t="n">
-        <v>9502547861.6</v>
+        <v>-3691678548.76</v>
       </c>
       <c r="AE5" t="n">
-        <v>-2269833695.99</v>
+        <v>3189004381.3</v>
       </c>
       <c r="AF5" t="n">
-        <v>-6981595227.28</v>
+        <v>-325543784.34</v>
       </c>
       <c r="AG5" t="n">
-        <v>378559075.93</v>
+        <v>350491504.01</v>
       </c>
       <c r="AH5" t="n">
-        <v>251694687.84</v>
+        <v>402276302.97</v>
       </c>
       <c r="AI5" t="n">
-        <v>19282738.73</v>
+        <v>140920294.94</v>
       </c>
       <c r="AJ5" t="n">
-        <v>232411949.11</v>
+        <v>261356008.03</v>
       </c>
       <c r="AK5" t="n">
-        <v>-46120214.16</v>
+        <v>-34213194.45</v>
       </c>
       <c r="AL5" t="n">
-        <v>-5550839.46</v>
+        <v>-5772761.21</v>
       </c>
       <c r="AM5" t="n">
-        <v>1951649681.2</v>
+        <v>593603080.6</v>
       </c>
       <c r="AN5" t="n">
-        <v>1071994237.59</v>
+        <v>1140237944.85</v>
       </c>
       <c r="AO5" t="n">
-        <v>-5335021957.08</v>
+        <v>-1271256502.29</v>
       </c>
       <c r="AP5" t="n">
-        <v>-20678894982.29</v>
+        <v>-19582015160.72</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-881109128.53</v>
+        <v>-1318213065.75</v>
       </c>
       <c r="AR5" t="n">
-        <v>-1890420022.1</v>
+        <v>-2166407604.2</v>
       </c>
       <c r="AS5" t="n">
-        <v>-17907365831.66</v>
+        <v>-16097394490.77</v>
       </c>
       <c r="AT5" t="n">
-        <v>27085911176.96</v>
+        <v>21993509607.86</v>
       </c>
       <c r="AU5" t="n">
-        <v>305625165.99</v>
+        <v>244242904.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>26780286010.97</v>
+        <v>21749266703.83</v>
       </c>
     </row>
   </sheetData>
@@ -3536,7 +3536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EQ2"/>
+  <dimension ref="A1:ER2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3707,570 +3707,575 @@
       </c>
       <c r="AH1" t="inlineStr">
         <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
           <t>trailingPE</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>forwardPE</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>volume</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>regularMarketVolume</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>averageVolume</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>averageVolume10days</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>averageDailyVolume10Day</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>bid</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>ask</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>bidSize</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>askSize</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>marketCap</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>nonDilutedMarketCap</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLow</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHigh</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>allTimeHigh</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>allTimeLow</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>priceToSalesTrailing12Months</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>fiftyDayAverage</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>twoHundredDayAverage</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>trailingAnnualDividendRate</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>trailingAnnualDividendYield</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>tradeable</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>enterpriseValue</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>profitMargins</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>floatShares</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>sharesOutstanding</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>heldPercentInsiders</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>heldPercentInstitutions</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>impliedSharesOutstanding</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>bookValue</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>priceToBook</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>lastFiscalYearEnd</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>nextFiscalYearEnd</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>mostRecentQuarter</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>netIncomeToCommon</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>trailingEps</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>forwardEps</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>lastSplitFactor</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>lastSplitDate</t>
         </is>
       </c>
-      <c r="BW1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>enterpriseToRevenue</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>enterpriseToEbitda</t>
         </is>
       </c>
-      <c r="BY1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>52WeekChange</t>
         </is>
       </c>
-      <c r="BZ1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>SandP52WeekChange</t>
         </is>
       </c>
-      <c r="CA1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>lastDividendValue</t>
         </is>
       </c>
-      <c r="CB1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>lastDividendDate</t>
         </is>
       </c>
-      <c r="CC1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>quoteType</t>
         </is>
       </c>
-      <c r="CD1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>currentPrice</t>
         </is>
       </c>
-      <c r="CE1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>recommendationKey</t>
         </is>
       </c>
-      <c r="CF1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>totalCash</t>
         </is>
       </c>
-      <c r="CG1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>totalCashPerShare</t>
         </is>
       </c>
-      <c r="CH1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>ebitda</t>
         </is>
       </c>
-      <c r="CI1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>totalDebt</t>
         </is>
       </c>
-      <c r="CJ1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>quickRatio</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>currentRatio</t>
         </is>
       </c>
-      <c r="CL1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>totalRevenue</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>debtToEquity</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>revenuePerShare</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>returnOnAssets</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>returnOnEquity</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>grossProfits</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>freeCashflow</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>operatingCashflow</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>revenueGrowth</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>grossMargins</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>ebitdaMargins</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>operatingMargins</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>financialCurrency</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>symbol</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>typeDisp</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>quoteSourceName</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>triggerable</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>customPriceAlertConfidence</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
         <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="EP1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="EQ1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
+      <c r="ER1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -4372,34 +4377,34 @@
         <v>4</v>
       </c>
       <c r="U2" t="n">
-        <v>3.5</v>
+        <v>3.39</v>
       </c>
       <c r="V2" t="n">
-        <v>3.28</v>
+        <v>3.44</v>
       </c>
       <c r="W2" t="n">
-        <v>3.51</v>
+        <v>3.2</v>
       </c>
       <c r="X2" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.5</v>
+        <v>3.39</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.28</v>
+        <v>3.44</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.51</v>
+        <v>3.2</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="AC2" t="n">
         <v>0.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="AE2" t="n">
         <v>1752192000</v>
@@ -4411,391 +4416,394 @@
         <v>5.69</v>
       </c>
       <c r="AH2" t="n">
-        <v>96.25</v>
+        <v>0.591</v>
       </c>
       <c r="AI2" t="n">
-        <v>7.129629</v>
+        <v>83.25</v>
       </c>
       <c r="AJ2" t="n">
-        <v>124390008</v>
+        <v>6.1666665</v>
       </c>
       <c r="AK2" t="n">
-        <v>124390008</v>
+        <v>30587731</v>
       </c>
       <c r="AL2" t="n">
-        <v>22160098</v>
+        <v>30587731</v>
       </c>
       <c r="AM2" t="n">
-        <v>26668268</v>
+        <v>29719475</v>
       </c>
       <c r="AN2" t="n">
-        <v>26668268</v>
+        <v>40812729</v>
       </c>
       <c r="AO2" t="n">
-        <v>3.85</v>
+        <v>40812729</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>7193899520</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>7193899920</v>
+        <v>6222256128</v>
       </c>
       <c r="AU2" t="n">
+        <v>6334369021</v>
+      </c>
+      <c r="AV2" t="n">
         <v>3.18</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="AW2" t="n">
         <v>4.88</v>
       </c>
-      <c r="AW2" t="n">
+      <c r="AX2" t="n">
         <v>16.346153</v>
       </c>
-      <c r="AX2" t="n">
+      <c r="AY2" t="n">
         <v>0.86025</v>
       </c>
-      <c r="AY2" t="n">
-        <v>0.30867445</v>
-      </c>
       <c r="AZ2" t="n">
-        <v>3.5404</v>
+        <v>0.26698336</v>
       </c>
       <c r="BA2" t="n">
-        <v>3.7645</v>
+        <v>3.5282</v>
       </c>
       <c r="BB2" t="n">
+        <v>3.75805</v>
+      </c>
+      <c r="BC2" t="n">
         <v>0.036</v>
       </c>
-      <c r="BC2" t="n">
-        <v>0.010285714</v>
-      </c>
-      <c r="BD2" t="inlineStr">
+      <c r="BD2" t="n">
+        <v>0.010619468</v>
+      </c>
+      <c r="BE2" t="inlineStr">
         <is>
           <t>CNY</t>
         </is>
       </c>
-      <c r="BE2" t="b">
+      <c r="BF2" t="b">
         <v>0</v>
       </c>
-      <c r="BF2" t="n">
-        <v>15000165376</v>
-      </c>
       <c r="BG2" t="n">
+        <v>14041564160</v>
+      </c>
+      <c r="BH2" t="n">
         <v>0.00686</v>
       </c>
-      <c r="BH2" t="n">
-        <v>1111372903</v>
-      </c>
       <c r="BI2" t="n">
+        <v>1113279370</v>
+      </c>
+      <c r="BJ2" t="n">
         <v>1868545434</v>
       </c>
-      <c r="BJ2" t="n">
+      <c r="BK2" t="n">
         <v>0.41724998</v>
       </c>
-      <c r="BK2" t="n">
+      <c r="BL2" t="n">
         <v>0.03694</v>
       </c>
-      <c r="BL2" t="n">
+      <c r="BM2" t="n">
         <v>1868545434</v>
       </c>
-      <c r="BM2" t="n">
-        <v>7.743</v>
-      </c>
       <c r="BN2" t="n">
-        <v>0.4972233</v>
+        <v>6.018</v>
       </c>
       <c r="BO2" t="n">
+        <v>0.55333996</v>
+      </c>
+      <c r="BP2" t="n">
         <v>1767139200</v>
       </c>
-      <c r="BP2" t="n">
+      <c r="BQ2" t="n">
         <v>1798675200</v>
       </c>
-      <c r="BQ2" t="n">
+      <c r="BR2" t="n">
         <v>1774915200</v>
       </c>
-      <c r="BR2" t="n">
+      <c r="BS2" t="n">
         <v>159785456</v>
       </c>
-      <c r="BS2" t="n">
+      <c r="BT2" t="n">
         <v>0.04</v>
       </c>
-      <c r="BT2" t="n">
+      <c r="BU2" t="n">
         <v>0.54</v>
       </c>
-      <c r="BU2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
         <is>
           <t>1.3:1</t>
         </is>
       </c>
-      <c r="BV2" t="n">
+      <c r="BW2" t="n">
         <v>1560988800</v>
       </c>
-      <c r="BW2" t="n">
-        <v>0.644</v>
-      </c>
       <c r="BX2" t="n">
-        <v>16.11</v>
+        <v>0.602</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.09065151</v>
+        <v>15.689</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.27697718</v>
+        <v>-0.023054779</v>
       </c>
       <c r="CA2" t="n">
+        <v>0.24487448</v>
+      </c>
+      <c r="CB2" t="n">
         <v>0.1</v>
       </c>
-      <c r="CB2" t="n">
+      <c r="CC2" t="n">
         <v>1752192000</v>
       </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
         <is>
           <t>EQUITY</t>
         </is>
       </c>
-      <c r="CD2" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="CE2" t="inlineStr">
+      <c r="CE2" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="CF2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="CF2" t="n">
+      <c r="CG2" t="n">
         <v>9339856896</v>
       </c>
-      <c r="CG2" t="n">
-        <v>5.008</v>
-      </c>
       <c r="CH2" t="n">
-        <v>931088576</v>
+        <v>4.998</v>
       </c>
       <c r="CI2" t="n">
+        <v>894999040</v>
+      </c>
+      <c r="CJ2" t="n">
         <v>16946219008</v>
       </c>
-      <c r="CJ2" t="n">
+      <c r="CK2" t="n">
         <v>1.033</v>
       </c>
-      <c r="CK2" t="n">
+      <c r="CL2" t="n">
         <v>1.56</v>
       </c>
-      <c r="CL2" t="n">
+      <c r="CM2" t="n">
         <v>23305781248</v>
       </c>
-      <c r="CM2" t="n">
+      <c r="CN2" t="n">
         <v>115.638</v>
       </c>
-      <c r="CN2" t="n">
-        <v>7.251</v>
-      </c>
       <c r="CO2" t="n">
-        <v>0.00574</v>
+        <v>12.473</v>
       </c>
       <c r="CP2" t="n">
+        <v>0.0053600003</v>
+      </c>
+      <c r="CQ2" t="n">
         <v>-0.00261</v>
       </c>
-      <c r="CQ2" t="n">
+      <c r="CR2" t="n">
         <v>1895710464</v>
       </c>
-      <c r="CR2" t="n">
-        <v>2240345856</v>
-      </c>
       <c r="CS2" t="n">
+        <v>2211343872</v>
+      </c>
+      <c r="CT2" t="n">
         <v>1599968128</v>
       </c>
-      <c r="CT2" t="n">
+      <c r="CU2" t="n">
         <v>0.279</v>
       </c>
-      <c r="CU2" t="n">
+      <c r="CV2" t="n">
         <v>0.08134</v>
       </c>
-      <c r="CV2" t="n">
-        <v>0.03995</v>
-      </c>
       <c r="CW2" t="n">
-        <v>0.02207</v>
-      </c>
-      <c r="CX2" t="inlineStr">
+        <v>0.038399998</v>
+      </c>
+      <c r="CX2" t="n">
+        <v>0.011089999</v>
+      </c>
+      <c r="CY2" t="inlineStr">
         <is>
           <t>CNY</t>
         </is>
       </c>
-      <c r="CY2" t="inlineStr">
+      <c r="CZ2" t="inlineStr">
         <is>
           <t>000090.SZ</t>
         </is>
       </c>
-      <c r="CZ2" t="inlineStr">
+      <c r="DA2" t="inlineStr">
         <is>
           <t>en-US</t>
         </is>
       </c>
-      <c r="DA2" t="inlineStr">
+      <c r="DB2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="DB2" t="inlineStr">
+      <c r="DC2" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="DC2" t="inlineStr">
+      <c r="DD2" t="inlineStr">
         <is>
           <t>Delayed Quote</t>
         </is>
       </c>
-      <c r="DD2" t="b">
+      <c r="DE2" t="b">
         <v>0</v>
       </c>
-      <c r="DE2" t="inlineStr">
+      <c r="DF2" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="DF2" t="inlineStr">
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>Shenzhen</t>
+        </is>
+      </c>
+      <c r="DH2" t="n">
+        <v>29719475</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>0.14999986</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>0.047169764</v>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>3.18 - 4.88</t>
+        </is>
+      </c>
+      <c r="DL2" t="n">
+        <v>-1.5500002</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>-0.317623</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>-2.3054779</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>1651229940</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>1651492800</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>-0.19819999</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>-0.05617595</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>-0.42805004</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>-0.11390217</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DY2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DZ2" t="inlineStr">
         <is>
           <t>SHENZHEN TAGEN GROUP CO LTD</t>
         </is>
       </c>
-      <c r="DG2" t="inlineStr">
+      <c r="EA2" t="inlineStr">
         <is>
           <t>Shenzhen Tagen Group Co., Ltd.</t>
         </is>
       </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="DI2" t="n">
-        <v>9.999997</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="DK2" t="inlineStr">
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>SHZ</t>
+        </is>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>finmb_6465470</t>
+        </is>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>Asia/Shanghai</t>
+        </is>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>CST</t>
+        </is>
+      </c>
+      <c r="EF2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="EG2" t="inlineStr">
+        <is>
+          <t>cn_market</t>
+        </is>
+      </c>
+      <c r="EH2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="EJ2" t="n">
+        <v>-1.7699168</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="EL2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DL2" t="n">
-        <v>1780038264</v>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>SHZ</t>
-        </is>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>finmb_6465470</t>
-        </is>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>Asia/Shanghai</t>
-        </is>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>CST</t>
-        </is>
-      </c>
-      <c r="DQ2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>cn_market</t>
-        </is>
-      </c>
-      <c r="DS2" t="b">
+      <c r="EM2" t="n">
+        <v>1782111885</v>
+      </c>
+      <c r="EN2" t="b">
         <v>0</v>
       </c>
-      <c r="DT2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DU2" t="n">
+      <c r="EO2" t="n">
         <v>932520600000</v>
       </c>
-      <c r="DV2" t="n">
-        <v>0.3499999</v>
-      </c>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>3.51 - 3.85</t>
-        </is>
-      </c>
-      <c r="DX2" t="inlineStr">
-        <is>
-          <t>Shenzhen</t>
-        </is>
-      </c>
-      <c r="DY2" t="n">
-        <v>22160098</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>0.66999984</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>0.21069176</v>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>3.18 - 4.88</t>
-        </is>
-      </c>
-      <c r="EC2" t="n">
-        <v>-1.0300002</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>-0.2110656</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>9.065151</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>1651229940</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>1651492800</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>0.30959988</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>0.08744771</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>0.08550000000000001</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>0.02271218</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EO2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EP2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EQ2" t="inlineStr"/>
+      <c r="EP2" t="n">
+        <v>-0.06000018</v>
+      </c>
+      <c r="EQ2" t="inlineStr">
+        <is>
+          <t>3.2 - 3.4</t>
+        </is>
+      </c>
+      <c r="ER2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
